--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CFA2D8-142C-9E48-91CF-34A60FAC535F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9962A61-46A6-924C-A8B2-0A48FDE119C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farmacias" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="115">
   <si>
     <t>name</t>
   </si>
@@ -306,6 +306,66 @@
   </si>
   <si>
     <t>(2901) 425-045</t>
+  </si>
+  <si>
+    <t>Farmacia Previley III</t>
+  </si>
+  <si>
+    <t>Av. Luro 3804</t>
+  </si>
+  <si>
+    <t>Mar del Plata</t>
+  </si>
+  <si>
+    <t>(223) 540-6049</t>
+  </si>
+  <si>
+    <t>Farmacia Azanza</t>
+  </si>
+  <si>
+    <t>San Martín 3001</t>
+  </si>
+  <si>
+    <t>(342) 525-6633</t>
+  </si>
+  <si>
+    <t>Farmacia Zorich</t>
+  </si>
+  <si>
+    <t>Calle 7 y 54</t>
+  </si>
+  <si>
+    <t>La Plata</t>
+  </si>
+  <si>
+    <t>Farmacia Inglesa</t>
+  </si>
+  <si>
+    <t>Calle 47 Nro. 634</t>
+  </si>
+  <si>
+    <t>Farmacia La Doce</t>
+  </si>
+  <si>
+    <t>Calle 12 Nro. 1307</t>
+  </si>
+  <si>
+    <t>Farmacia Caruso</t>
+  </si>
+  <si>
+    <t>Calle 44 Nro. 549</t>
+  </si>
+  <si>
+    <t>(221) 421-4133</t>
+  </si>
+  <si>
+    <t>(221) 421-3400</t>
+  </si>
+  <si>
+    <t>(221) 489-0991</t>
+  </si>
+  <si>
+    <t>(221) 439-2600</t>
   </si>
 </sst>
 </file>
@@ -369,13 +429,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -390,7 +449,20 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -404,10 +476,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J17">
-  <autoFilter ref="A1:J17" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J16">
-    <sortCondition ref="A9:A16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J23">
+  <autoFilter ref="A1:J23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J21">
+    <sortCondition ref="A9:A21"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -415,10 +487,10 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="locality"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="city"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="province"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="whatsapp"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="whatsappDisplay"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="phone"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="phoneDisplay"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="whatsapp" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="whatsappDisplay" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="phone" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="phoneDisplay" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -710,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -772,12 +844,14 @@
       <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -795,10 +869,12 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="4">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3">
         <v>1153530030</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="3" t="s">
         <v>65</v>
       </c>
     </row>
@@ -818,10 +894,12 @@
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="4">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>1147873100</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -841,10 +919,12 @@
       <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="4">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>1139854640</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -864,11 +944,12 @@
       <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="H6" s="4">
+      <c r="F6" s="4"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>1148015544</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
@@ -888,10 +969,12 @@
       <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="5">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4">
         <v>1143221001</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="3" t="s">
         <v>77</v>
       </c>
     </row>
@@ -911,10 +994,12 @@
       <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="5">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4">
         <v>1143286544</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="3" t="s">
         <v>78</v>
       </c>
     </row>
@@ -934,10 +1019,12 @@
       <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="H9" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -957,10 +1044,12 @@
       <c r="E10" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="4">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3">
         <v>1155547975</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -980,16 +1069,16 @@
       <c r="E11" t="s">
         <v>13</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1009,16 +1098,16 @@
       <c r="E12" t="s">
         <v>13</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1038,10 +1127,12 @@
       <c r="E13" t="s">
         <v>13</v>
       </c>
-      <c r="H13" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="3" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1061,91 +1152,245 @@
       <c r="E14" t="s">
         <v>31</v>
       </c>
-      <c r="H14" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" t="s">
-        <v>46</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2235406049</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" t="s">
-        <v>52</v>
+        <v>31</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3">
+        <v>2214214133</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3">
+        <v>2214213400</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3">
+        <v>2214890991</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3">
+        <v>2214392600</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3425256633</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>89</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B23" t="s">
         <v>90</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C23" t="s">
         <v>91</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D23" t="s">
         <v>91</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E23" t="s">
         <v>92</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F23" s="5">
         <v>2901584008</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H23" s="3">
         <v>2901425045</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>94</v>
       </c>
     </row>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9962A61-46A6-924C-A8B2-0A48FDE119C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C499C2-FA4D-1E40-8816-3C4063976AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="147">
   <si>
     <t>name</t>
   </si>
@@ -68,9 +68,6 @@
     <t>01145051010</t>
   </si>
   <si>
-    <t>FarmaStar - Consulte por envíos</t>
-  </si>
-  <si>
     <t>Saavedra</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>(0230) 447-3005</t>
   </si>
   <si>
-    <t>FarmaTotal</t>
-  </si>
-  <si>
     <t>J.V. Zapata 303 (esq. Rioja)</t>
   </si>
   <si>
@@ -278,9 +272,6 @@
     <t>(11) 4787-2100</t>
   </si>
   <si>
-    <t>Farmacia Azul</t>
-  </si>
-  <si>
     <t>Av. Entre Rios 299</t>
   </si>
   <si>
@@ -366,6 +357,111 @@
   </si>
   <si>
     <t>(221) 439-2600</t>
+  </si>
+  <si>
+    <t>Farmacia Soy Tu Farmacia - Soy Larrea</t>
+  </si>
+  <si>
+    <t>Larrea 906</t>
+  </si>
+  <si>
+    <t>(11)49611441</t>
+  </si>
+  <si>
+    <t>Farmacia Farmarket</t>
+  </si>
+  <si>
+    <t>S. M. de Tucumán</t>
+  </si>
+  <si>
+    <t>Tucumán</t>
+  </si>
+  <si>
+    <t>Mendoza 382</t>
+  </si>
+  <si>
+    <t>(381) 422-2879</t>
+  </si>
+  <si>
+    <t>FarmaStar -  Consulte por envíos -</t>
+  </si>
+  <si>
+    <t>FarmaTotal  - 15% Descuento a Particulares -</t>
+  </si>
+  <si>
+    <t>Farmacia Azul  - 20% Descuento a Particulares -</t>
+  </si>
+  <si>
+    <t>Oncativo 1366</t>
+  </si>
+  <si>
+    <t>B. Gral. Paz</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>(3516) 02-0243</t>
+  </si>
+  <si>
+    <t>Farmacia Líder 258</t>
+  </si>
+  <si>
+    <t>Farmacia Líder Oncativo</t>
+  </si>
+  <si>
+    <t>Av. Gral. Paz 258</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>Farmacia Líder Cerro</t>
+  </si>
+  <si>
+    <t>Av. Rafael Nuñez 4220</t>
+  </si>
+  <si>
+    <t>Cerro de las Rosas</t>
+  </si>
+  <si>
+    <t>Naciones Unidas 925</t>
+  </si>
+  <si>
+    <t>B. Parque V. Sarsfield</t>
+  </si>
+  <si>
+    <t>Farmacia Sanchez Antoniolli - SA 6</t>
+  </si>
+  <si>
+    <t>Farmacia Sanchez Antoniolli - SA 16</t>
+  </si>
+  <si>
+    <t>Av. Carlos Gauss 590</t>
+  </si>
+  <si>
+    <t>B. Villa Belgrano</t>
+  </si>
+  <si>
+    <t>Farmacia Sanchez Antoniolli - SA 31</t>
+  </si>
+  <si>
+    <t>Av. Patria 617</t>
+  </si>
+  <si>
+    <t>(351) 817-3000</t>
+  </si>
+  <si>
+    <t>Farmacia Maria Auxiliadora</t>
+  </si>
+  <si>
+    <t>Av. España 546</t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>(266) 442-0907</t>
   </si>
 </sst>
 </file>
@@ -429,7 +525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -444,6 +540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -476,10 +573,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J23">
-  <autoFilter ref="A1:J23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J21">
-    <sortCondition ref="A9:A21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J32">
+  <autoFilter ref="A1:J32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
+    <sortCondition ref="A9:A22"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -782,10 +879,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="39.83203125" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
@@ -830,38 +927,38 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -875,18 +972,18 @@
         <v>1153530030</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -900,18 +997,18 @@
         <v>1147873100</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
         <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -925,18 +1022,18 @@
         <v>1139854640</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -950,18 +1047,18 @@
         <v>1148015544</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -975,18 +1072,18 @@
         <v>1143221001</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1000,43 +1097,43 @@
         <v>1143286544</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>35</v>
       </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
         <v>66</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1050,47 +1147,47 @@
         <v>1155547975</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -1099,27 +1196,27 @@
         <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1129,279 +1226,511 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
+      <c r="H13" s="3">
+        <v>1149611441</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="3">
-        <v>2235406049</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3">
-        <v>2214214133</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2235406049</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3">
-        <v>2214213400</v>
+        <v>2214214133</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3">
-        <v>2214890991</v>
+        <v>2214213400</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3">
+        <v>2214890991</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3">
         <v>2214392600</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="I20" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
         <v>40</v>
       </c>
-      <c r="C20" t="s">
+      <c r="F21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="G21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="3" t="s">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="B22" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="C22" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
         <v>48</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="G22" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3425256633</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3425256633</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
         <v>89</v>
       </c>
-      <c r="B23" t="s">
+      <c r="F24" s="5">
+        <v>2901584008</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C23" t="s">
+      <c r="H24" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>94</v>
-      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3516020243</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3516020243</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="3">
+        <v>3516020243</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F37" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
     <hyperlink ref="H8" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
+    <hyperlink ref="H25" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I25" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1416,47 +1745,47 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C499C2-FA4D-1E40-8816-3C4063976AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADACF884-8789-6D45-8853-7FDDB2F8F620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="155">
   <si>
     <t>name</t>
   </si>
@@ -359,9 +359,6 @@
     <t>(221) 439-2600</t>
   </si>
   <si>
-    <t>Farmacia Soy Tu Farmacia - Soy Larrea</t>
-  </si>
-  <si>
     <t>Larrea 906</t>
   </si>
   <si>
@@ -395,9 +392,6 @@
     <t>Oncativo 1366</t>
   </si>
   <si>
-    <t>B. Gral. Paz</t>
-  </si>
-  <si>
     <t>Córdoba</t>
   </si>
   <si>
@@ -428,9 +422,6 @@
     <t>Naciones Unidas 925</t>
   </si>
   <si>
-    <t>B. Parque V. Sarsfield</t>
-  </si>
-  <si>
     <t>Farmacia Sanchez Antoniolli - SA 6</t>
   </si>
   <si>
@@ -440,9 +431,6 @@
     <t>Av. Carlos Gauss 590</t>
   </si>
   <si>
-    <t>B. Villa Belgrano</t>
-  </si>
-  <si>
     <t>Farmacia Sanchez Antoniolli - SA 31</t>
   </si>
   <si>
@@ -462,6 +450,42 @@
   </si>
   <si>
     <t>(266) 442-0907</t>
+  </si>
+  <si>
+    <t>Farmacia Zentner</t>
+  </si>
+  <si>
+    <t>San Jeronimo 3101</t>
+  </si>
+  <si>
+    <t>(342) 591-2681</t>
+  </si>
+  <si>
+    <t>B° Gral. Paz</t>
+  </si>
+  <si>
+    <t>B° Villa Belgrano</t>
+  </si>
+  <si>
+    <t>B° Parque V. Sarsfield</t>
+  </si>
+  <si>
+    <t>Farmacia Soy tu Farmacia - Soy Sanar 64</t>
+  </si>
+  <si>
+    <t>Av. Belgrano 2316</t>
+  </si>
+  <si>
+    <t>Sarandí</t>
+  </si>
+  <si>
+    <t>(11) 4430-2999</t>
+  </si>
+  <si>
+    <t>Farmacia Soy tu Farmacia - Soy Larrea</t>
+  </si>
+  <si>
+    <t>Avellaneda</t>
   </si>
 </sst>
 </file>
@@ -573,10 +597,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J32">
-  <autoFilter ref="A1:J32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
-    <sortCondition ref="A9:A22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J34">
+  <autoFilter ref="A1:J34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
+    <sortCondition ref="A9:A23"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -927,7 +951,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -1002,7 +1026,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
         <v>83</v>
@@ -1210,10 +1234,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" t="s">
         <v>112</v>
-      </c>
-      <c r="B13" t="s">
-        <v>113</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -1230,7 +1254,7 @@
         <v>1149611441</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1285,60 +1309,60 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="3">
-        <v>2235406049</v>
+        <v>1144302999</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3">
-        <v>2214214133</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="F17" s="3">
+        <v>2235406049</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
         <v>101</v>
@@ -1352,18 +1376,18 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3">
-        <v>2214213400</v>
+        <v>2214214133</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
         <v>101</v>
@@ -1377,18 +1401,18 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3">
-        <v>2214890991</v>
+        <v>2214213400</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
         <v>101</v>
@@ -1402,330 +1426,380 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3">
-        <v>2214392600</v>
+        <v>2214890991</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>43</v>
+        <v>30</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3">
+        <v>2214392600</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="3">
-        <v>3425256633</v>
+      <c r="F23" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>90</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="3">
-        <v>2901425045</v>
+        <v>3425912681</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="J25" s="3"/>
+        <v>89</v>
+      </c>
+      <c r="F25" s="5">
+        <v>2901584008</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
-      </c>
-      <c r="F26" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F27" s="3">
         <v>3516020243</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F28" s="3">
         <v>3516020243</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F29" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F30" s="3">
         <v>3518173000</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3">
         <v>3518173000</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>145</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3">
+        <v>123</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3">
         <v>2664420907</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="I33" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="3">
+        <v>3425256633</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F37" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
     <hyperlink ref="H8" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H25" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I25" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="H26" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I26" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADACF884-8789-6D45-8853-7FDDB2F8F620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3282F152-AF1D-D64E-B9FC-5E23F3FDB922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Farmacias" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="170">
   <si>
     <t>name</t>
   </si>
@@ -486,6 +499,51 @@
   </si>
   <si>
     <t>Avellaneda</t>
+  </si>
+  <si>
+    <t>Farmacia FarmaPlus</t>
+  </si>
+  <si>
+    <t>25 de Mayo 707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrientes </t>
+  </si>
+  <si>
+    <t>Corrientes</t>
+  </si>
+  <si>
+    <t>(379) 472-5782</t>
+  </si>
+  <si>
+    <t>Farmacia Capital</t>
+  </si>
+  <si>
+    <t>Av. Maipú 249</t>
+  </si>
+  <si>
+    <t>(379) 488-6003</t>
+  </si>
+  <si>
+    <t>Farmacia Lipstein</t>
+  </si>
+  <si>
+    <t>Juan Molina 397</t>
+  </si>
+  <si>
+    <t>Bahía Blanca</t>
+  </si>
+  <si>
+    <t>(2915) 71-8813</t>
+  </si>
+  <si>
+    <t>12 de Octubre 3792</t>
+  </si>
+  <si>
+    <t>(223) 544-9668</t>
+  </si>
+  <si>
+    <t>Farmacia Previley II</t>
   </si>
 </sst>
 </file>
@@ -549,7 +607,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -565,6 +623,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -597,10 +656,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J34">
-  <autoFilter ref="A1:J34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
-    <sortCondition ref="A9:A23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J38">
+  <autoFilter ref="A1:J38" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
+    <sortCondition ref="A9:A25"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -903,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.83203125" customWidth="1"/>
@@ -1359,60 +1418,60 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3">
-        <v>2214214133</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="F18" s="4">
+        <v>2235449668</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3">
-        <v>2214213400</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="F19" s="3">
+        <v>2915718813</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
         <v>101</v>
@@ -1426,18 +1485,18 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3">
-        <v>2214890991</v>
+        <v>2214214133</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
         <v>101</v>
@@ -1451,205 +1510,205 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3">
-        <v>2214392600</v>
+        <v>2214213400</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>43</v>
+        <v>30</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3">
+        <v>2214890991</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
+        <v>2214392600</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3">
-        <v>3425912681</v>
+        <v>40</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="5">
-        <v>2901584008</v>
+        <v>48</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>91</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="J26" s="3"/>
+      <c r="H26" s="3">
+        <v>3425912681</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>123</v>
-      </c>
-      <c r="F27" s="3">
-        <v>3516020243</v>
+        <v>89</v>
+      </c>
+      <c r="F27" s="5">
+        <v>2901584008</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
         <v>123</v>
@@ -1668,13 +1727,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>123</v>
@@ -1683,23 +1742,23 @@
         <v>123</v>
       </c>
       <c r="F30" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>123</v>
@@ -1708,23 +1767,23 @@
         <v>123</v>
       </c>
       <c r="F31" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D32" t="s">
         <v>123</v>
@@ -1743,68 +1802,170 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
-        <v>141</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>142</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="F33" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="F34" s="3">
-        <v>3425256633</v>
+        <v>3518173000</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" t="s">
+        <v>158</v>
+      </c>
+      <c r="E35" t="s">
+        <v>158</v>
+      </c>
+      <c r="F35" s="3">
+        <v>3794725782</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F36" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+    </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F37" s="6"/>
+      <c r="A37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="3">
+        <v>3425256633</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F39" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
     <hyperlink ref="H8" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H26" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I26" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="H28" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I28" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="F18" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
+    <hyperlink ref="G18" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3282F152-AF1D-D64E-B9FC-5E23F3FDB922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7B6FD4-F22D-1143-B406-5316926EAF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29260" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farmacias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="172">
   <si>
     <t>name</t>
   </si>
@@ -312,9 +312,6 @@
     <t>(2901) 425-045</t>
   </si>
   <si>
-    <t>Farmacia Previley III</t>
-  </si>
-  <si>
     <t>Av. Luro 3804</t>
   </si>
   <si>
@@ -324,15 +321,6 @@
     <t>(223) 540-6049</t>
   </si>
   <si>
-    <t>Farmacia Azanza</t>
-  </si>
-  <si>
-    <t>San Martín 3001</t>
-  </si>
-  <si>
-    <t>(342) 525-6633</t>
-  </si>
-  <si>
     <t>Farmacia Zorich</t>
   </si>
   <si>
@@ -543,14 +531,32 @@
     <t>(223) 544-9668</t>
   </si>
   <si>
-    <t>Farmacia Previley II</t>
+    <t>Farmacia Previley III - 15% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Previley II - 15% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Del Milagro</t>
+  </si>
+  <si>
+    <t>Arturo Illia 676</t>
+  </si>
+  <si>
+    <t>Resistencia</t>
+  </si>
+  <si>
+    <t>Chaco</t>
+  </si>
+  <si>
+    <t>(362) 562-8866</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,8 +586,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,12 +606,31 @@
         <fgColor rgb="FFE6F3F4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CCE4"/>
+        <bgColor rgb="FFB8CCE4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -607,7 +639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -622,8 +654,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -962,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.83203125" customWidth="1"/>
@@ -1010,7 +1050,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -1085,7 +1125,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B5" t="s">
         <v>83</v>
@@ -1293,10 +1333,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -1313,7 +1353,7 @@
         <v>1149611441</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1368,16 +1408,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" t="s">
         <v>150</v>
-      </c>
-      <c r="C16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D16" t="s">
-        <v>154</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -1386,23 +1426,23 @@
         <v>1144302999</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" t="s">
         <v>92</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>93</v>
       </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -1411,23 +1451,23 @@
         <v>2235406049</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -1435,24 +1475,24 @@
       <c r="F18" s="4">
         <v>2235449668</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>168</v>
+      <c r="G18" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -1461,23 +1501,23 @@
         <v>2915718813</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -1488,21 +1528,21 @@
         <v>2214214133</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
@@ -1513,21 +1553,21 @@
         <v>2214213400</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -1538,21 +1578,21 @@
         <v>2214890991</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -1563,12 +1603,12 @@
         <v>2214392600</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
@@ -1622,10 +1662,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
         <v>48</v>
@@ -1642,7 +1682,7 @@
         <v>3425912681</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1676,245 +1716,245 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="4">
         <v>3814222879</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>118</v>
+      <c r="I28" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F29" s="3">
         <v>3516020243</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F30" s="3">
         <v>3516020243</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F31" s="3">
         <v>3516020243</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F32" s="3">
         <v>3518173000</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F33" s="3">
         <v>3518173000</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F34" s="3">
         <v>3518173000</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F35" s="3">
         <v>3794725782</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F36" s="3">
         <v>3794886003</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -1922,36 +1962,37 @@
         <v>2664420907</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="3">
-        <v>3425256633</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F39" s="6"/>
+        <v>170</v>
+      </c>
+      <c r="F38" s="7">
+        <v>3625628866</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="3">
+        <v>3625427244</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>171</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7B6FD4-F22D-1143-B406-5316926EAF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3E2459-E591-D242-B560-C731355CE78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29260" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="175">
   <si>
     <t>name</t>
   </si>
@@ -550,6 +550,15 @@
   </si>
   <si>
     <t>(362) 562-8866</t>
+  </si>
+  <si>
+    <t>Farmacia Azanza</t>
+  </si>
+  <si>
+    <t>San Martin 3001</t>
+  </si>
+  <si>
+    <t>(342) 525-6633</t>
   </si>
 </sst>
 </file>
@@ -696,8 +705,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J38">
-  <autoFilter ref="A1:J38" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J39">
+  <autoFilter ref="A1:J39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
     <sortCondition ref="A9:A25"/>
   </sortState>
@@ -1002,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.83203125" customWidth="1"/>
@@ -1687,93 +1696,93 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>91</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F27" s="6">
+        <v>3425256633</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
-        <v>112</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="J28" s="3"/>
+        <v>89</v>
+      </c>
+      <c r="F28" s="5">
+        <v>2901584008</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
-        <v>119</v>
-      </c>
-      <c r="F29" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
         <v>119</v>
@@ -1792,13 +1801,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
         <v>119</v>
@@ -1817,13 +1826,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
         <v>119</v>
@@ -1832,23 +1841,23 @@
         <v>119</v>
       </c>
       <c r="F32" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D33" t="s">
         <v>119</v>
@@ -1867,13 +1876,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
         <v>119</v>
@@ -1892,35 +1901,35 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="E35" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="F35" s="3">
-        <v>3794725782</v>
+        <v>3518173000</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
         <v>153</v>
@@ -1932,65 +1941,90 @@
         <v>154</v>
       </c>
       <c r="F36" s="3">
-        <v>3794886003</v>
+        <v>3794725782</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>138</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="F37" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>167</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>168</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>169</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>169</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E39" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F39" s="7">
         <v>3625628866</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G39" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H39" s="3">
         <v>3625427244</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I39" s="8" t="s">
         <v>171</v>
       </c>
     </row>
@@ -1998,15 +2032,17 @@
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
     <hyperlink ref="H8" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H28" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I28" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="H29" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I29" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
     <hyperlink ref="F18" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
     <hyperlink ref="G18" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
+    <hyperlink ref="F27" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
+    <hyperlink ref="G27" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3E2459-E591-D242-B560-C731355CE78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2AAF20-A9BF-0246-9A81-F2383FE2E1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29260" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="187">
   <si>
     <t>name</t>
   </si>
@@ -559,6 +559,42 @@
   </si>
   <si>
     <t>(342) 525-6633</t>
+  </si>
+  <si>
+    <t>Farmacia Lombardelli</t>
+  </si>
+  <si>
+    <t>Farmacia Lagos</t>
+  </si>
+  <si>
+    <t>Farmacia Cubo</t>
+  </si>
+  <si>
+    <t>Av. Pellegrini 1795</t>
+  </si>
+  <si>
+    <t>0341 720-5889</t>
+  </si>
+  <si>
+    <t>(341) 720-5889</t>
+  </si>
+  <si>
+    <t>Av. Ovidio Lagos 1399</t>
+  </si>
+  <si>
+    <t>0341 449-8660</t>
+  </si>
+  <si>
+    <t>(341) 449-8660</t>
+  </si>
+  <si>
+    <t>Mendoza 2595</t>
+  </si>
+  <si>
+    <t>0341 4210769</t>
+  </si>
+  <si>
+    <t>(341) 4210769</t>
   </si>
 </sst>
 </file>
@@ -705,8 +741,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J39">
-  <autoFilter ref="A1:J39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J42">
+  <autoFilter ref="A1:J42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
     <sortCondition ref="A9:A25"/>
   </sortState>
@@ -1011,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.83203125" customWidth="1"/>
@@ -1671,193 +1707,193 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3">
-        <v>3425912681</v>
+      <c r="H26" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="6">
-        <v>3425256633</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>91</v>
+        <v>48</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="J29" s="3"/>
+      <c r="H29" s="3">
+        <v>3425912681</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="F30" s="6">
+        <v>3425256633</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="3">
-        <v>3516020243</v>
+        <v>89</v>
+      </c>
+      <c r="F31" s="5">
+        <v>2901584008</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
         <v>119</v>
@@ -1866,23 +1902,23 @@
         <v>119</v>
       </c>
       <c r="F33" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
         <v>119</v>
@@ -1891,23 +1927,23 @@
         <v>119</v>
       </c>
       <c r="F34" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
         <v>119</v>
@@ -1916,115 +1952,190 @@
         <v>119</v>
       </c>
       <c r="F35" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="F36" s="3">
-        <v>3794725782</v>
+        <v>3518173000</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D37" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="F37" s="3">
-        <v>3794886003</v>
+        <v>3518173000</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>138</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="F38" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="3">
+        <v>3794725782</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" t="s">
+        <v>154</v>
+      </c>
+      <c r="E40" t="s">
+        <v>154</v>
+      </c>
+      <c r="F40" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>137</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>167</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B42" t="s">
         <v>168</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C42" t="s">
         <v>169</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D42" t="s">
         <v>169</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E42" t="s">
         <v>170</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F42" s="7">
         <v>3625628866</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G42" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H42" s="3">
         <v>3625427244</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I42" s="8" t="s">
         <v>171</v>
       </c>
     </row>
@@ -2032,17 +2143,21 @@
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
     <hyperlink ref="H8" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H29" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I29" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="H32" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I32" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
     <hyperlink ref="F18" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
     <hyperlink ref="G18" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
-    <hyperlink ref="F27" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
-    <hyperlink ref="G27" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
+    <hyperlink ref="F30" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
+    <hyperlink ref="G30" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
+    <hyperlink ref="H28" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
+    <hyperlink ref="I28" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
+    <hyperlink ref="H27" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
+    <hyperlink ref="I27" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2AAF20-A9BF-0246-9A81-F2383FE2E1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC9D720-F894-D04E-92F3-7F05CFB39833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29260" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5780" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farmacias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="194">
   <si>
     <t>name</t>
   </si>
@@ -381,15 +381,6 @@
     <t>(381) 422-2879</t>
   </si>
   <si>
-    <t>FarmaStar -  Consulte por envíos -</t>
-  </si>
-  <si>
-    <t>FarmaTotal  - 15% Descuento a Particulares -</t>
-  </si>
-  <si>
-    <t>Farmacia Azul  - 20% Descuento a Particulares -</t>
-  </si>
-  <si>
     <t>Oncativo 1366</t>
   </si>
   <si>
@@ -561,15 +552,6 @@
     <t>(342) 525-6633</t>
   </si>
   <si>
-    <t>Farmacia Lombardelli</t>
-  </si>
-  <si>
-    <t>Farmacia Lagos</t>
-  </si>
-  <si>
-    <t>Farmacia Cubo</t>
-  </si>
-  <si>
     <t>Av. Pellegrini 1795</t>
   </si>
   <si>
@@ -595,6 +577,45 @@
   </si>
   <si>
     <t>(341) 4210769</t>
+  </si>
+  <si>
+    <t>Farmacity</t>
+  </si>
+  <si>
+    <t>Av. Córdoba 4601</t>
+  </si>
+  <si>
+    <t>Av. Belgrano 1194</t>
+  </si>
+  <si>
+    <t>Farmacia Lombardelli - 20% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Lagos - 20% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Cubo - 20% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Chester - 20% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Azul  - 20% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>FarmaTotal  - 15% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>FarmaStar</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>San Martin 2066</t>
+  </si>
+  <si>
+    <t>(261) 4637400</t>
   </si>
 </sst>
 </file>
@@ -741,10 +762,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J42">
-  <autoFilter ref="A1:J42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
-    <sortCondition ref="A9:A25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J45">
+  <autoFilter ref="A1:J45" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J28">
+    <sortCondition ref="A11:A28"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -1047,10 +1068,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.83203125" customWidth="1"/>
+    <col min="1" max="1" width="41.1640625" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
@@ -1095,7 +1116,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -1170,7 +1191,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="B5" t="s">
         <v>83</v>
@@ -1195,13 +1216,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1209,24 +1230,20 @@
       <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3">
-        <v>1148015544</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1236,22 +1253,18 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="4">
-        <v>1143221001</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -1259,49 +1272,49 @@
       <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="4">
-        <v>1143286544</v>
+      <c r="H8" s="3">
+        <v>1148015544</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>36</v>
+      <c r="H9" s="4">
+        <v>1143221001</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1311,51 +1324,47 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3">
-        <v>1155547975</v>
+      <c r="H10" s="4">
+        <v>1143286544</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>23</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -1363,14 +1372,10 @@
       <c r="E12" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>24</v>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3">
+        <v>1155547975</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>25</v>
@@ -1378,13 +1383,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1392,24 +1397,28 @@
       <c r="E13" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>1149611441</v>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
@@ -1417,196 +1426,200 @@
       <c r="E14" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="H14" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
+      <c r="H15" s="3">
+        <v>1149611441</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1144302999</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="3">
-        <v>2235406049</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="4">
-        <v>2235449668</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>164</v>
+      <c r="F18" s="3">
+        <v>1144302999</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="3">
-        <v>2915718813</v>
+        <v>2235406049</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3">
-        <v>2214214133</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F20" s="4">
+        <v>2235449668</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3">
-        <v>2214213400</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F21" s="3">
+        <v>2915718813</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
         <v>97</v>
@@ -1620,18 +1633,18 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3">
-        <v>2214890991</v>
+        <v>2214214133</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
         <v>97</v>
@@ -1645,122 +1658,122 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3">
+        <v>2214213400</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3">
+        <v>2214890991</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3">
         <v>2214392600</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" t="s">
         <v>38</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
         <v>39</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D26" t="s">
         <v>39</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E26" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2614637400</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>45</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B28" t="s">
         <v>46</v>
-      </c>
-      <c r="C25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>175</v>
-      </c>
-      <c r="B26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>176</v>
-      </c>
-      <c r="B27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>177</v>
-      </c>
-      <c r="B28" t="s">
-        <v>178</v>
       </c>
       <c r="C28" t="s">
         <v>47</v>
@@ -1771,388 +1784,467 @@
       <c r="E28" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
         <v>48</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3">
-        <v>3425912681</v>
+      <c r="H29" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="6">
-        <v>3425256633</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H32" s="3">
+        <v>3425912681</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="E33" t="s">
-        <v>119</v>
-      </c>
-      <c r="F33" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="F33" s="4">
+        <v>3425256633</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="D34" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="5">
+        <v>2901584008</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>119</v>
       </c>
-      <c r="E34" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="3">
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="3">
         <v>3516020243</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" t="s">
-        <v>119</v>
-      </c>
-      <c r="F35" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F36" s="3">
-        <v>3518173000</v>
-      </c>
       <c r="G36" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F37" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F38" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E39" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="F39" s="3">
-        <v>3794725782</v>
+        <v>3518173000</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D40" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E40" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="F40" s="3">
-        <v>3794886003</v>
+        <v>3518173000</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3794725782</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B44" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" t="s">
+        <v>134</v>
+      </c>
+      <c r="E44" t="s">
+        <v>134</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B41" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" t="s">
-        <v>137</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" t="s">
         <v>167</v>
       </c>
-      <c r="B42" t="s">
+      <c r="F45" s="7">
+        <v>3625628866</v>
+      </c>
+      <c r="G45" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C42" t="s">
-        <v>169</v>
-      </c>
-      <c r="D42" t="s">
-        <v>169</v>
-      </c>
-      <c r="E42" t="s">
-        <v>170</v>
-      </c>
-      <c r="F42" s="7">
-        <v>3625628866</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="H45" s="3">
         <v>3625427244</v>
       </c>
-      <c r="I42" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="I45" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H7" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
-    <hyperlink ref="H8" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H32" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I32" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
-    <hyperlink ref="F18" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
-    <hyperlink ref="G18" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
-    <hyperlink ref="F30" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
-    <hyperlink ref="G30" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
-    <hyperlink ref="H28" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
-    <hyperlink ref="I28" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
-    <hyperlink ref="H27" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
-    <hyperlink ref="I27" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
+    <hyperlink ref="H9" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
+    <hyperlink ref="H10" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
+    <hyperlink ref="H35" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I35" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="F20" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
+    <hyperlink ref="G20" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
+    <hyperlink ref="F33" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
+    <hyperlink ref="G33" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
+    <hyperlink ref="H31" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
+    <hyperlink ref="I31" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
+    <hyperlink ref="H30" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
+    <hyperlink ref="I30" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC9D720-F894-D04E-92F3-7F05CFB39833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56491B64-4BA5-1E48-B538-C229B87856C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5780" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="199">
   <si>
     <t>name</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Farmaet</t>
   </si>
   <si>
-    <t>Av. San Martin 6946</t>
-  </si>
-  <si>
     <t>Villa Devoto</t>
   </si>
   <si>
@@ -612,10 +609,28 @@
     <t>Godoy Cruz</t>
   </si>
   <si>
-    <t>San Martin 2066</t>
-  </si>
-  <si>
     <t>(261) 4637400</t>
+  </si>
+  <si>
+    <t>Farmacia Farma Uco</t>
+  </si>
+  <si>
+    <t>San Martín 1283</t>
+  </si>
+  <si>
+    <t>San Martín 2066</t>
+  </si>
+  <si>
+    <t>Av. San Martín 6946</t>
+  </si>
+  <si>
+    <t>Tunuyán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendoza    </t>
+  </si>
+  <si>
+    <t>(2622) 42-5585</t>
   </si>
 </sst>
 </file>
@@ -762,10 +777,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J45">
-  <autoFilter ref="A1:J45" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J28">
-    <sortCondition ref="A11:A28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J46">
+  <autoFilter ref="A1:J46" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J29">
+    <sortCondition ref="A11:A29"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -1068,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -1116,44 +1131,44 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
         <v>60</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>61</v>
       </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -1161,24 +1176,24 @@
         <v>1153530030</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
         <v>77</v>
       </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -1186,24 +1201,24 @@
         <v>1147873100</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -1211,24 +1226,24 @@
         <v>1139854640</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" t="s">
         <v>181</v>
       </c>
-      <c r="B6" t="s">
-        <v>182</v>
-      </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -1237,19 +1252,19 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -1258,19 +1273,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
         <v>79</v>
       </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="3"/>
@@ -1278,24 +1293,24 @@
         <v>1148015544</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -1303,24 +1318,24 @@
         <v>1143221001</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -1328,49 +1343,49 @@
         <v>1143286544</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
         <v>64</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>65</v>
       </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -1378,82 +1393,82 @@
         <v>1155547975</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -1461,7 +1476,7 @@
         <v>1149611441</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1469,166 +1484,166 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" t="s">
         <v>11</v>
       </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
         <v>28</v>
       </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
         <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" t="s">
         <v>142</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>143</v>
       </c>
-      <c r="C18" t="s">
-        <v>144</v>
-      </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" s="3">
         <v>1144302999</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
         <v>92</v>
       </c>
-      <c r="C19" t="s">
-        <v>93</v>
-      </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" s="3">
         <v>2235406049</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20" s="4">
         <v>2235449668</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" t="s">
         <v>156</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>157</v>
       </c>
-      <c r="C21" t="s">
-        <v>158</v>
-      </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21" s="3">
         <v>2915718813</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s">
         <v>95</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>96</v>
       </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1636,24 +1651,24 @@
         <v>2214214133</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" t="s">
         <v>98</v>
       </c>
-      <c r="B23" t="s">
-        <v>99</v>
-      </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1661,24 +1676,24 @@
         <v>2214213400</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" t="s">
         <v>100</v>
       </c>
-      <c r="B24" t="s">
-        <v>101</v>
-      </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1686,24 +1701,24 @@
         <v>2214890991</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" t="s">
         <v>102</v>
       </c>
-      <c r="B25" t="s">
-        <v>103</v>
-      </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1711,545 +1726,572 @@
         <v>2214392600</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
         <v>38</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" t="s">
         <v>39</v>
       </c>
-      <c r="D26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" t="s">
         <v>39</v>
-      </c>
-      <c r="E27" t="s">
-        <v>40</v>
       </c>
       <c r="F27" s="3">
         <v>2614637400</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4">
+        <v>2622425585</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" t="s">
         <v>47</v>
       </c>
-      <c r="D29" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>180</v>
-      </c>
+      <c r="G29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
         <v>47</v>
-      </c>
-      <c r="D30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" t="s">
-        <v>48</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>177</v>
+      <c r="H30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
         <v>47</v>
-      </c>
-      <c r="D31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3">
-        <v>3425912681</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>138</v>
+      <c r="H32" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="4">
-        <v>3425256633</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3">
+        <v>3425912681</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>91</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F34" s="4">
+        <v>3425256633</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="J35" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="F35" s="5">
+        <v>2901584008</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
-      </c>
-      <c r="F36" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F37" s="3">
         <v>3516020243</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F38" s="3">
         <v>3516020243</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="3">
+        <v>3516020243</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="E39" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="3">
-        <v>3518173000</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
         <v>140</v>
       </c>
       <c r="D40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F40" s="3">
         <v>3518173000</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C41" t="s">
         <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F41" s="3">
         <v>3518173000</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="E42" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="F42" s="3">
-        <v>3794725782</v>
+        <v>3518173000</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" t="s">
         <v>150</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="3">
+        <v>3794725782</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="E43" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="3">
-        <v>3794886003</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="E44" t="s">
-        <v>134</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F44" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" t="s">
         <v>164</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C46" t="s">
         <v>165</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D46" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" t="s">
         <v>166</v>
       </c>
-      <c r="D45" t="s">
-        <v>166</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F46" s="7">
+        <v>3625628866</v>
+      </c>
+      <c r="G46" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="7">
-        <v>3625628866</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H46" s="3">
         <v>3625427244</v>
       </c>
-      <c r="I45" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="I46" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H9" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
     <hyperlink ref="H10" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H35" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I35" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="H36" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I36" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
     <hyperlink ref="F20" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
     <hyperlink ref="G20" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
-    <hyperlink ref="F33" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
-    <hyperlink ref="G33" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
-    <hyperlink ref="H31" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
-    <hyperlink ref="I31" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
-    <hyperlink ref="H30" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
-    <hyperlink ref="I30" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
+    <hyperlink ref="F34" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
+    <hyperlink ref="G34" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
+    <hyperlink ref="H32" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
+    <hyperlink ref="I32" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
+    <hyperlink ref="H31" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
+    <hyperlink ref="I31" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
+    <hyperlink ref="H28" r:id="rId13" display="tel:(02622) 42-5585" xr:uid="{3BBF1536-921E-6741-9023-473CF19052A5}"/>
+    <hyperlink ref="I28" r:id="rId14" display="tel:(02622) 42-5585" xr:uid="{0B4D10C9-136D-4C4F-9997-41F7B999118F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2264,47 +2306,47 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56491B64-4BA5-1E48-B538-C229B87856C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99C691E-75F4-6E4F-98CD-2C2CE754F43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5780" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farmacias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="208">
   <si>
     <t>name</t>
   </si>
@@ -585,15 +585,6 @@
     <t>Av. Belgrano 1194</t>
   </si>
   <si>
-    <t>Farmacia Lombardelli - 20% Descuento a Particulares</t>
-  </si>
-  <si>
-    <t>Farmacia Lagos - 20% Descuento a Particulares</t>
-  </si>
-  <si>
-    <t>Farmacia Cubo - 20% Descuento a Particulares</t>
-  </si>
-  <si>
     <t>Farmacia Chester - 20% Descuento a Particulares</t>
   </si>
   <si>
@@ -631,6 +622,42 @@
   </si>
   <si>
     <t>(2622) 42-5585</t>
+  </si>
+  <si>
+    <t>Farmacia Lombardelli - 40% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Lagos - 40% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Cubo - 40% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Av. Corrientes 3930</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Farmacity - Primera Junta</t>
+  </si>
+  <si>
+    <t>Av. Rivadavia 5375</t>
+  </si>
+  <si>
+    <t>Farmacity - Medrano</t>
+  </si>
+  <si>
+    <t>Farmacity - Canning</t>
+  </si>
+  <si>
+    <t>Farmacity - Callao</t>
+  </si>
+  <si>
+    <t>Av. Corrientes 1820</t>
+  </si>
+  <si>
+    <t>Caballito</t>
   </si>
 </sst>
 </file>
@@ -777,10 +804,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J46">
-  <autoFilter ref="A1:J46" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J29">
-    <sortCondition ref="A11:A29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J49">
+  <autoFilter ref="A1:J49" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J32">
+    <sortCondition ref="A14:A32"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -1083,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -1131,7 +1158,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -1206,7 +1233,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B5" t="s">
         <v>82</v>
@@ -1231,7 +1258,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
         <v>181</v>
@@ -1273,13 +1300,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>200</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1287,24 +1314,20 @@
       <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>1148015544</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>207</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1314,22 +1337,18 @@
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="4">
-        <v>1143221001</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1339,47 +1358,43 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="4">
-        <v>1143286544</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F11" s="4"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>35</v>
+      <c r="H11" s="3">
+        <v>1148015544</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1389,22 +1404,22 @@
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3">
-        <v>1155547975</v>
+      <c r="H12" s="4">
+        <v>1143221001</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1412,57 +1427,49 @@
       <c r="E13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>23</v>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4">
+        <v>1143286544</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
@@ -1473,21 +1480,21 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
-        <v>1149611441</v>
+        <v>1155547975</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -1495,221 +1502,229 @@
       <c r="E16" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="H16" s="3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1144302999</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3">
+        <v>1149611441</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2235406049</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="4">
-        <v>2235449668</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="3">
-        <v>2915718813</v>
+        <v>1144302999</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3">
-        <v>2214214133</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="F22" s="3">
+        <v>2235406049</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3">
-        <v>2214213400</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="F23" s="4">
+        <v>2235449668</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3">
-        <v>2214890991</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="F24" s="3">
+        <v>2915718813</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
         <v>96</v>
@@ -1723,172 +1738,172 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3">
-        <v>2214392600</v>
+        <v>2214214133</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
+        <v>2214213400</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="3">
-        <v>2614637400</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3">
+        <v>2214890991</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="4">
-        <v>2622425585</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>198</v>
+      <c r="H28" s="3">
+        <v>2214392600</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>183</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>179</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F30" s="3">
+        <v>2614637400</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>193</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>176</v>
+      <c r="H31" s="4">
+        <v>2622425585</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1899,204 +1914,204 @@
       <c r="E32" t="s">
         <v>47</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>173</v>
-      </c>
+      <c r="F32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
         <v>47</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3">
-        <v>3425912681</v>
+      <c r="H33" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="4">
-        <v>3425256633</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H35" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>90</v>
+        <v>47</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="E36" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J36" s="3"/>
+      <c r="H36" s="3">
+        <v>3425912681</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>116</v>
+        <v>47</v>
+      </c>
+      <c r="F37" s="4">
+        <v>3425256633</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F38" s="3">
-        <v>3516020243</v>
+        <v>88</v>
+      </c>
+      <c r="F38" s="5">
+        <v>2901584008</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+        <v>89</v>
+      </c>
+      <c r="H38" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E39" t="s">
-        <v>115</v>
-      </c>
-      <c r="F39" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
         <v>115</v>
@@ -2105,23 +2120,23 @@
         <v>115</v>
       </c>
       <c r="F40" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
         <v>115</v>
@@ -2130,23 +2145,23 @@
         <v>115</v>
       </c>
       <c r="F41" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D42" t="s">
         <v>115</v>
@@ -2155,138 +2170,213 @@
         <v>115</v>
       </c>
       <c r="F42" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E43" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F43" s="3">
-        <v>3794725782</v>
+        <v>3518173000</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E44" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F44" s="3">
-        <v>3794886003</v>
+        <v>3518173000</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E45" t="s">
-        <v>133</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3518173000</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" s="3">
+        <v>3794725782</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>163</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B49" t="s">
         <v>164</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C49" t="s">
         <v>165</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D49" t="s">
         <v>165</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E49" t="s">
         <v>166</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F49" s="7">
         <v>3625628866</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G49" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H49" s="3">
         <v>3625427244</v>
       </c>
-      <c r="I46" s="8" t="s">
+      <c r="I49" s="8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H9" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
-    <hyperlink ref="H10" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H36" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I36" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
-    <hyperlink ref="F20" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
-    <hyperlink ref="G20" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
-    <hyperlink ref="F34" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
-    <hyperlink ref="G34" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
-    <hyperlink ref="H32" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
-    <hyperlink ref="I32" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
-    <hyperlink ref="H31" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
-    <hyperlink ref="I31" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
-    <hyperlink ref="H28" r:id="rId13" display="tel:(02622) 42-5585" xr:uid="{3BBF1536-921E-6741-9023-473CF19052A5}"/>
-    <hyperlink ref="I28" r:id="rId14" display="tel:(02622) 42-5585" xr:uid="{0B4D10C9-136D-4C4F-9997-41F7B999118F}"/>
+    <hyperlink ref="H12" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
+    <hyperlink ref="H13" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
+    <hyperlink ref="H39" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I39" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="F23" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
+    <hyperlink ref="G23" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
+    <hyperlink ref="F37" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
+    <hyperlink ref="G37" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
+    <hyperlink ref="H35" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
+    <hyperlink ref="I35" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
+    <hyperlink ref="H34" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
+    <hyperlink ref="I34" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
+    <hyperlink ref="H31" r:id="rId13" display="tel:(02622) 42-5585" xr:uid="{3BBF1536-921E-6741-9023-473CF19052A5}"/>
+    <hyperlink ref="I31" r:id="rId14" display="tel:(02622) 42-5585" xr:uid="{0B4D10C9-136D-4C4F-9997-41F7B999118F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99C691E-75F4-6E4F-98CD-2C2CE754F43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12AA3B0-54B6-9B42-A491-2871DA1FB9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2420" yWindow="-19280" windowWidth="28760" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farmacias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="214">
   <si>
     <t>name</t>
   </si>
@@ -658,6 +658,24 @@
   </si>
   <si>
     <t>Caballito</t>
+  </si>
+  <si>
+    <t>Farmacia Plazoleta</t>
+  </si>
+  <si>
+    <t>Av. República del Libano 999</t>
+  </si>
+  <si>
+    <t>(381) 423-7198</t>
+  </si>
+  <si>
+    <t>Nahuel Huapi 4281</t>
+  </si>
+  <si>
+    <t>Villa Urquiza</t>
+  </si>
+  <si>
+    <t>(11) 2479-1770</t>
   </si>
 </sst>
 </file>
@@ -804,10 +822,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J49">
-  <autoFilter ref="A1:J49" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J32">
-    <sortCondition ref="A14:A32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J51">
+  <autoFilter ref="A1:J51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J33">
+    <sortCondition ref="A15:A33"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -1110,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -1183,13 +1201,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>212</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1197,21 +1215,21 @@
       <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>1153530030</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="F3" s="3">
+        <v>1124791770</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
         <v>61</v>
@@ -1225,21 +1243,21 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3">
-        <v>1147873100</v>
+        <v>1153530030</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -1250,21 +1268,21 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3">
-        <v>1139854640</v>
+        <v>1147873100</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1274,18 +1292,22 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="3">
+        <v>1139854640</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -1300,13 +1322,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1321,13 +1343,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1342,13 +1364,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1363,13 +1385,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1377,24 +1399,20 @@
       <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3">
-        <v>1148015544</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1402,21 +1420,21 @@
       <c r="E12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="4">
-        <v>1143221001</v>
+      <c r="H12" s="3">
+        <v>1148015544</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
@@ -1430,71 +1448,71 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="4">
-        <v>1143286544</v>
+        <v>1143221001</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
-        <v>35</v>
+      <c r="H14" s="4">
+        <v>1143286544</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3">
-        <v>1155547975</v>
+      <c r="H15" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -1502,14 +1520,10 @@
       <c r="E16" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>23</v>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3">
+        <v>1155547975</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>24</v>
@@ -1517,13 +1531,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1546,10 +1560,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -1560,24 +1574,28 @@
       <c r="E18" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3">
-        <v>1149611441</v>
+      <c r="F18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
@@ -1587,94 +1605,94 @@
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>13</v>
+      <c r="H19" s="3">
+        <v>1149611441</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="3">
-        <v>1144302999</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="3">
-        <v>2235406049</v>
+        <v>1144302999</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
         <v>92</v>
@@ -1685,71 +1703,71 @@
       <c r="E23" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="4">
-        <v>2235449668</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>160</v>
+      <c r="F23" s="3">
+        <v>2235406049</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C24" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="3">
-        <v>2915718813</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>158</v>
+      <c r="F24" s="4">
+        <v>2235449668</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3">
-        <v>2214214133</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="F25" s="3">
+        <v>2915718813</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
         <v>96</v>
@@ -1763,18 +1781,18 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3">
-        <v>2214213400</v>
+        <v>2214214133</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
         <v>96</v>
@@ -1788,18 +1806,18 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3">
-        <v>2214890991</v>
+        <v>2214213400</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
         <v>96</v>
@@ -1813,50 +1831,46 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3">
-        <v>2214392600</v>
+        <v>2214890991</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3">
+        <v>2214392600</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
         <v>38</v>
@@ -1864,71 +1878,75 @@
       <c r="E30" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="3">
-        <v>2614637400</v>
+      <c r="F30" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D31" t="s">
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4">
-        <v>2622425585</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>195</v>
-      </c>
+      <c r="F31" s="3">
+        <v>2614637400</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>193</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="4">
+        <v>2622425585</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1939,21 +1957,21 @@
       <c r="E33" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>179</v>
-      </c>
+      <c r="F33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1966,19 +1984,19 @@
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>176</v>
+      <c r="H34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B35" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1992,43 +2010,43 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
         <v>47</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3">
-        <v>3425912681</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>137</v>
+      <c r="H36" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
         <v>47</v>
@@ -2039,129 +2057,130 @@
       <c r="E37" t="s">
         <v>47</v>
       </c>
-      <c r="F37" s="4">
-        <v>3425256633</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3">
+        <v>3425912681</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="E38" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H38" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>90</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F38" s="4">
+        <v>3425256633</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E39" t="s">
-        <v>111</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J39" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="F39" s="5">
+        <v>2901584008</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E40" t="s">
-        <v>115</v>
-      </c>
-      <c r="F40" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4">
+        <v>3814222879</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>208</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="4">
+        <v>3814237198</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
         <v>115</v>
@@ -2180,13 +2199,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D43" t="s">
         <v>115</v>
@@ -2195,23 +2214,23 @@
         <v>115</v>
       </c>
       <c r="F43" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -2220,23 +2239,23 @@
         <v>115</v>
       </c>
       <c r="F44" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
         <v>115</v>
@@ -2255,128 +2274,178 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E46" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F46" s="3">
-        <v>3794725782</v>
+        <v>3518173000</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E47" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F47" s="3">
-        <v>3794886003</v>
+        <v>3518173000</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C48" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="E48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3794725782</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D49" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E49" t="s">
-        <v>166</v>
-      </c>
-      <c r="F49" s="7">
-        <v>3625628866</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3625427244</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>167</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" t="s">
+        <v>133</v>
+      </c>
+      <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>133</v>
+      </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
+      <c r="H50" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" t="s">
+        <v>165</v>
+      </c>
+      <c r="E51" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" s="7">
+        <v>3625628866</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" s="3">
+        <v>3625427244</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H12" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
-    <hyperlink ref="H13" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H39" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I39" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
-    <hyperlink ref="F23" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
-    <hyperlink ref="G23" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
-    <hyperlink ref="F37" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
-    <hyperlink ref="G37" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
-    <hyperlink ref="H35" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
-    <hyperlink ref="I35" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
-    <hyperlink ref="H34" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
-    <hyperlink ref="I34" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
-    <hyperlink ref="H31" r:id="rId13" display="tel:(02622) 42-5585" xr:uid="{3BBF1536-921E-6741-9023-473CF19052A5}"/>
-    <hyperlink ref="I31" r:id="rId14" display="tel:(02622) 42-5585" xr:uid="{0B4D10C9-136D-4C4F-9997-41F7B999118F}"/>
+    <hyperlink ref="H13" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
+    <hyperlink ref="H14" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
+    <hyperlink ref="H40" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I40" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="F24" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
+    <hyperlink ref="G24" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
+    <hyperlink ref="F38" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
+    <hyperlink ref="G38" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
+    <hyperlink ref="H36" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
+    <hyperlink ref="I36" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
+    <hyperlink ref="H35" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
+    <hyperlink ref="I35" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
+    <hyperlink ref="H32" r:id="rId13" display="tel:(02622) 42-5585" xr:uid="{3BBF1536-921E-6741-9023-473CF19052A5}"/>
+    <hyperlink ref="I32" r:id="rId14" display="tel:(02622) 42-5585" xr:uid="{0B4D10C9-136D-4C4F-9997-41F7B999118F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
